--- a/artfynd/A 29596-2025 artfynd.xlsx
+++ b/artfynd/A 29596-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AZ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706819</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706822</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706825</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706837</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706844</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1409,6 +1439,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708952</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1516,6 +1551,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708960</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1623,6 +1663,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708972</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1730,6 +1775,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708976</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1837,6 +1887,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708980</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1963,6 +2018,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706820</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2089,6 +2149,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706824</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2215,6 +2280,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706829</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2341,6 +2411,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706830</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2467,6 +2542,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706831</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2593,6 +2673,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706834</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2719,6 +2804,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706848</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2826,6 +2916,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708948</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2933,6 +3028,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708950</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3040,6 +3140,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708953</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3147,6 +3252,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708962</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3254,6 +3364,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708963</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3361,6 +3476,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708968</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3468,6 +3588,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708971</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3575,6 +3700,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708973</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3682,6 +3812,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708978</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3789,6 +3924,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708981</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3896,6 +4036,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708986</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4007,6 +4152,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708936</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4114,6 +4264,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708959</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4221,6 +4376,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708974</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4347,6 +4507,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708933</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4473,6 +4638,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706814</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4599,6 +4769,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706821</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4725,6 +4900,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706840</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4832,6 +5012,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708951</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4939,6 +5124,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708961</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5046,6 +5236,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708969</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5172,6 +5367,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706808</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5298,6 +5498,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706810</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5424,6 +5629,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706813</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5550,6 +5760,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706832</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5657,6 +5872,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708924</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5783,6 +6003,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708929</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5909,6 +6134,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708932</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6035,6 +6265,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708935</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6161,6 +6396,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708940</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6287,6 +6527,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708942</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6413,6 +6658,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708946</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6539,6 +6789,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708965</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6665,6 +6920,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708944</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6791,6 +7051,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708945</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6917,6 +7182,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706809</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7043,6 +7313,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706816</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7169,6 +7444,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706817</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7295,6 +7575,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706833</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7421,6 +7706,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706852</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7547,6 +7837,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706855</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7673,6 +7968,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708925</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7799,6 +8099,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708930</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7925,6 +8230,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708937</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8051,6 +8361,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708939</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8177,6 +8492,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708964</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8303,6 +8623,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708975</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8429,6 +8754,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708982</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8555,6 +8885,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708983</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8666,6 +9001,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706815</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8773,6 +9113,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708979</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8899,6 +9244,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708926</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9025,6 +9375,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708928</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9140,6 +9495,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706826</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9255,6 +9615,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706842</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9370,6 +9735,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706850</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9485,6 +9855,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708931</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9600,6 +9975,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708941</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9715,6 +10095,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708949</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9835,6 +10220,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706827</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9955,6 +10345,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708943</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10083,6 +10478,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708954</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10215,6 +10615,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708955</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10335,6 +10740,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708967</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10455,6 +10865,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708989</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10570,6 +10985,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708947</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10694,6 +11114,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708923</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10818,6 +11243,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708988</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10934,6 +11364,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706857</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11060,6 +11495,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708927</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11168,8 +11608,103 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134708987</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>